--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1CF0ED-667F-470E-BEFD-20E24ED9426F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348071E3-649E-4B1F-B5C7-FAFA20EA77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Mariami</t>
   </si>
   <si>
-    <t>23/08/1991</t>
+    <t>23/08/1991 00:00:00</t>
   </si>
   <si>
     <t>Géorgie</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>20/11/2025 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>ABDOU</t>
@@ -79,13 +79,13 @@
     <t>Houfranie</t>
   </si>
   <si>
-    <t>31/12/1978</t>
+    <t>31/12/1978 00:00:00</t>
   </si>
   <si>
     <t>Comores</t>
   </si>
   <si>
-    <t>01/09/2025</t>
+    <t>01/09/2025 00:00:00</t>
   </si>
   <si>
     <t>AHED MOHAMED</t>
@@ -94,7 +94,7 @@
     <t>Mohamed</t>
   </si>
   <si>
-    <t>22/07/1993</t>
+    <t>22/07/1993 00:00:00</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -103,7 +103,7 @@
     <t>M</t>
   </si>
   <si>
-    <t>01/05/2024</t>
+    <t>01/05/2024 00:00:00</t>
   </si>
   <si>
     <t>ALHAJ</t>
@@ -112,10 +112,10 @@
     <t>Mudother</t>
   </si>
   <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
+    <t>08/04/1999 00:00:00</t>
+  </si>
+  <si>
+    <t>25/11/2024 00:00:00</t>
   </si>
   <si>
     <t>BEGUM</t>
@@ -124,13 +124,13 @@
     <t>Lima</t>
   </si>
   <si>
-    <t>10/12/1990</t>
+    <t>10/12/1990 00:00:00</t>
   </si>
   <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>25/09/2025</t>
+    <t>25/09/2025 00:00:00</t>
   </si>
   <si>
     <t>CHKHAPELIA</t>
@@ -139,10 +139,10 @@
     <t>Tamta</t>
   </si>
   <si>
-    <t>01/04/1992</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
+    <t>01/04/1992 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/2022 00:00:00</t>
   </si>
   <si>
     <t>DIAMPITISA</t>
@@ -151,13 +151,13 @@
     <t>Madalena</t>
   </si>
   <si>
-    <t>02/11/1967</t>
+    <t>02/11/1967 00:00:00</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>23/09/2025</t>
+    <t>23/09/2025 00:00:00</t>
   </si>
   <si>
     <t>EBRAHIM DUD</t>
@@ -166,7 +166,7 @@
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025</t>
+    <t>16/09/2025 00:00:00</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -175,7 +175,7 @@
     <t>Kiala Baptista</t>
   </si>
   <si>
-    <t>31/12/1994</t>
+    <t>31/12/1994 00:00:00</t>
   </si>
   <si>
     <t>ELIDRISSI BOUANANI</t>
@@ -184,13 +184,13 @@
     <t>Fatima</t>
   </si>
   <si>
-    <t>01/01/1959</t>
+    <t>01/01/1959 00:00:00</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>15/09/2022</t>
+    <t>15/09/2022 00:00:00</t>
   </si>
   <si>
     <t>FURAH KITAMBALA</t>
@@ -202,7 +202,7 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>26/11/2025</t>
+    <t>26/11/2025 00:00:00</t>
   </si>
   <si>
     <t>HASHEMI</t>
@@ -211,13 +211,13 @@
     <t>Asghar</t>
   </si>
   <si>
-    <t>28/02/1999</t>
+    <t>28/02/1999 00:00:00</t>
   </si>
   <si>
     <t>Afghanistan</t>
   </si>
   <si>
-    <t>09/10/2025</t>
+    <t>09/10/2025 00:00:00</t>
   </si>
   <si>
     <t>IMERI</t>
@@ -226,13 +226,13 @@
     <t>Mirela</t>
   </si>
   <si>
-    <t>30/05/1977</t>
+    <t>30/05/1977 00:00:00</t>
   </si>
   <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>10/05/2022</t>
+    <t>10/05/2022 00:00:00</t>
   </si>
   <si>
     <t>IREDIA</t>
@@ -241,7 +241,7 @@
     <t>Tracy</t>
   </si>
   <si>
-    <t>27/07/1982</t>
+    <t>27/07/1982 00:00:00</t>
   </si>
   <si>
     <t>Nigéria</t>
@@ -253,7 +253,7 @@
     <t>Febe</t>
   </si>
   <si>
-    <t>05/03/2001</t>
+    <t>05/03/2001 00:00:00</t>
   </si>
   <si>
     <t>JARA</t>
@@ -262,13 +262,13 @@
     <t>Mario</t>
   </si>
   <si>
-    <t>19/01/2003</t>
+    <t>19/01/2003 00:00:00</t>
   </si>
   <si>
     <t>Chili</t>
   </si>
   <si>
-    <t>18/09/2025</t>
+    <t>18/09/2025 00:00:00</t>
   </si>
   <si>
     <t>KINAVUIDI</t>
@@ -277,10 +277,10 @@
     <t>Viviane</t>
   </si>
   <si>
-    <t>29/06/1988</t>
-  </si>
-  <si>
-    <t>10/09/2025</t>
+    <t>29/06/1988 00:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2025 00:00:00</t>
   </si>
   <si>
     <t>LAGOUNE</t>
@@ -289,13 +289,13 @@
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002</t>
+    <t>15/08/2002 00:00:00</t>
   </si>
   <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025</t>
+    <t>07/11/2025 00:00:00</t>
   </si>
   <si>
     <t>LUMBE OMOWO</t>
@@ -304,10 +304,10 @@
     <t>Anne-Marie</t>
   </si>
   <si>
-    <t>18/03/1979</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
+    <t>18/03/1979 00:00:00</t>
+  </si>
+  <si>
+    <t>25/11/2025 00:00:00</t>
   </si>
   <si>
     <t>MADALENA</t>
@@ -316,10 +316,10 @@
     <t>Lidia</t>
   </si>
   <si>
-    <t>29/05/2018</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
+    <t>29/05/2018 00:00:00</t>
+  </si>
+  <si>
+    <t>14/11/2025 00:00:00</t>
   </si>
   <si>
     <t>MATETA</t>
@@ -328,7 +328,7 @@
     <t>Gloria</t>
   </si>
   <si>
-    <t>30/07/1994</t>
+    <t>30/07/1994 00:00:00</t>
   </si>
   <si>
     <t>NGELI</t>
@@ -337,7 +337,7 @@
     <t>Yolande</t>
   </si>
   <si>
-    <t>06/12/1980</t>
+    <t>06/12/1980 00:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">OLIVEIRA </t>
@@ -346,10 +346,10 @@
     <t>Laura</t>
   </si>
   <si>
-    <t>14/12/1986</t>
-  </si>
-  <si>
-    <t>02/06/2024</t>
+    <t>14/12/1986 00:00:00</t>
+  </si>
+  <si>
+    <t>02/06/2024 00:00:00</t>
   </si>
   <si>
     <t>RIAHI</t>
@@ -358,7 +358,7 @@
     <t>Souhail</t>
   </si>
   <si>
-    <t>13/11/1992</t>
+    <t>13/11/1992 00:00:00</t>
   </si>
   <si>
     <t>Tunisie</t>
@@ -370,13 +370,13 @@
     <t>Nawa</t>
   </si>
   <si>
-    <t>15/11/1996</t>
+    <t>15/11/1996 00:00:00</t>
   </si>
   <si>
     <t>Côte d'Ivoire</t>
   </si>
   <si>
-    <t>01/10/2024</t>
+    <t>01/10/2024 00:00:00</t>
   </si>
   <si>
     <t>TINIKASCHVILI</t>
@@ -385,10 +385,10 @@
     <t>Maka</t>
   </si>
   <si>
-    <t>21/09/1983</t>
-  </si>
-  <si>
-    <t>12/10/2021</t>
+    <t>21/09/1983 00:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2021 00:00:00</t>
   </si>
   <si>
     <t>TONOYAN</t>
@@ -397,13 +397,13 @@
     <t>Alvard</t>
   </si>
   <si>
-    <t>10/01/1963</t>
+    <t>10/01/1963 00:00:00</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>12/01/2016</t>
+    <t>12/01/2016 00:00:00</t>
   </si>
   <si>
     <t>VIUCHE GIRON</t>
@@ -412,13 +412,13 @@
     <t>Sanyi</t>
   </si>
   <si>
-    <t>21/05/1995</t>
+    <t>21/05/1995 00:00:00</t>
   </si>
   <si>
     <t>Colombie</t>
   </si>
   <si>
-    <t>06/03/2025</t>
+    <t>06/03/2025 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -905,7 +905,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348071E3-649E-4B1F-B5C7-FAFA20EA77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79B4D52-D08F-452D-ADD8-793EB28B59C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Mariami</t>
   </si>
   <si>
-    <t>23/08/1991 00:00:00</t>
+    <t>23/08/1991</t>
   </si>
   <si>
     <t>Géorgie</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>20/11/2025 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>ABDOU</t>
@@ -79,13 +79,13 @@
     <t>Houfranie</t>
   </si>
   <si>
-    <t>31/12/1978 00:00:00</t>
+    <t>31/12/1978</t>
   </si>
   <si>
     <t>Comores</t>
   </si>
   <si>
-    <t>01/09/2025 00:00:00</t>
+    <t>01/09/2025</t>
   </si>
   <si>
     <t>AHED MOHAMED</t>
@@ -94,7 +94,7 @@
     <t>Mohamed</t>
   </si>
   <si>
-    <t>22/07/1993 00:00:00</t>
+    <t>22/07/1993</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -103,7 +103,7 @@
     <t>M</t>
   </si>
   <si>
-    <t>01/05/2024 00:00:00</t>
+    <t>01/05/2024</t>
   </si>
   <si>
     <t>ALHAJ</t>
@@ -112,10 +112,10 @@
     <t>Mudother</t>
   </si>
   <si>
-    <t>08/04/1999 00:00:00</t>
-  </si>
-  <si>
-    <t>25/11/2024 00:00:00</t>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
   </si>
   <si>
     <t>BEGUM</t>
@@ -124,13 +124,13 @@
     <t>Lima</t>
   </si>
   <si>
-    <t>10/12/1990 00:00:00</t>
+    <t>10/12/1990</t>
   </si>
   <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>25/09/2025 00:00:00</t>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>CHKHAPELIA</t>
@@ -139,10 +139,10 @@
     <t>Tamta</t>
   </si>
   <si>
-    <t>01/04/1992 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/2022 00:00:00</t>
+    <t>01/04/1992</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
   </si>
   <si>
     <t>DIAMPITISA</t>
@@ -151,13 +151,13 @@
     <t>Madalena</t>
   </si>
   <si>
-    <t>02/11/1967 00:00:00</t>
+    <t>02/11/1967</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>23/09/2025 00:00:00</t>
+    <t>23/09/2025</t>
   </si>
   <si>
     <t>EBRAHIM DUD</t>
@@ -166,7 +166,7 @@
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025 00:00:00</t>
+    <t>16/09/2025</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -175,7 +175,7 @@
     <t>Kiala Baptista</t>
   </si>
   <si>
-    <t>31/12/1994 00:00:00</t>
+    <t>31/12/1994</t>
   </si>
   <si>
     <t>ELIDRISSI BOUANANI</t>
@@ -184,13 +184,13 @@
     <t>Fatima</t>
   </si>
   <si>
-    <t>01/01/1959 00:00:00</t>
+    <t>01/01/1959</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>15/09/2022 00:00:00</t>
+    <t>15/09/2022</t>
   </si>
   <si>
     <t>FURAH KITAMBALA</t>
@@ -202,7 +202,7 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>26/11/2025 00:00:00</t>
+    <t>26/11/2025</t>
   </si>
   <si>
     <t>HASHEMI</t>
@@ -211,13 +211,13 @@
     <t>Asghar</t>
   </si>
   <si>
-    <t>28/02/1999 00:00:00</t>
+    <t>28/02/1999</t>
   </si>
   <si>
     <t>Afghanistan</t>
   </si>
   <si>
-    <t>09/10/2025 00:00:00</t>
+    <t>09/10/2025</t>
   </si>
   <si>
     <t>IMERI</t>
@@ -226,13 +226,13 @@
     <t>Mirela</t>
   </si>
   <si>
-    <t>30/05/1977 00:00:00</t>
+    <t>30/05/1977</t>
   </si>
   <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>10/05/2022 00:00:00</t>
+    <t>10/05/2022</t>
   </si>
   <si>
     <t>IREDIA</t>
@@ -241,7 +241,7 @@
     <t>Tracy</t>
   </si>
   <si>
-    <t>27/07/1982 00:00:00</t>
+    <t>27/07/1982</t>
   </si>
   <si>
     <t>Nigéria</t>
@@ -253,7 +253,7 @@
     <t>Febe</t>
   </si>
   <si>
-    <t>05/03/2001 00:00:00</t>
+    <t>05/03/2001</t>
   </si>
   <si>
     <t>JARA</t>
@@ -262,13 +262,13 @@
     <t>Mario</t>
   </si>
   <si>
-    <t>19/01/2003 00:00:00</t>
+    <t>19/01/2003</t>
   </si>
   <si>
     <t>Chili</t>
   </si>
   <si>
-    <t>18/09/2025 00:00:00</t>
+    <t>18/09/2025</t>
   </si>
   <si>
     <t>KINAVUIDI</t>
@@ -277,10 +277,10 @@
     <t>Viviane</t>
   </si>
   <si>
-    <t>29/06/1988 00:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2025 00:00:00</t>
+    <t>29/06/1988</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
   </si>
   <si>
     <t>LAGOUNE</t>
@@ -289,13 +289,13 @@
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002 00:00:00</t>
+    <t>15/08/2002</t>
   </si>
   <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025 00:00:00</t>
+    <t>07/11/2025</t>
   </si>
   <si>
     <t>LUMBE OMOWO</t>
@@ -304,10 +304,10 @@
     <t>Anne-Marie</t>
   </si>
   <si>
-    <t>18/03/1979 00:00:00</t>
-  </si>
-  <si>
-    <t>25/11/2025 00:00:00</t>
+    <t>18/03/1979</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
   </si>
   <si>
     <t>MADALENA</t>
@@ -316,10 +316,10 @@
     <t>Lidia</t>
   </si>
   <si>
-    <t>29/05/2018 00:00:00</t>
-  </si>
-  <si>
-    <t>14/11/2025 00:00:00</t>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
   </si>
   <si>
     <t>MATETA</t>
@@ -328,7 +328,7 @@
     <t>Gloria</t>
   </si>
   <si>
-    <t>30/07/1994 00:00:00</t>
+    <t>30/07/1994</t>
   </si>
   <si>
     <t>NGELI</t>
@@ -337,7 +337,7 @@
     <t>Yolande</t>
   </si>
   <si>
-    <t>06/12/1980 00:00:00</t>
+    <t>06/12/1980</t>
   </si>
   <si>
     <t xml:space="preserve">OLIVEIRA </t>
@@ -346,10 +346,10 @@
     <t>Laura</t>
   </si>
   <si>
-    <t>14/12/1986 00:00:00</t>
-  </si>
-  <si>
-    <t>02/06/2024 00:00:00</t>
+    <t>14/12/1986</t>
+  </si>
+  <si>
+    <t>02/06/2024</t>
   </si>
   <si>
     <t>RIAHI</t>
@@ -358,7 +358,7 @@
     <t>Souhail</t>
   </si>
   <si>
-    <t>13/11/1992 00:00:00</t>
+    <t>13/11/1992</t>
   </si>
   <si>
     <t>Tunisie</t>
@@ -370,13 +370,13 @@
     <t>Nawa</t>
   </si>
   <si>
-    <t>15/11/1996 00:00:00</t>
+    <t>15/11/1996</t>
   </si>
   <si>
     <t>Côte d'Ivoire</t>
   </si>
   <si>
-    <t>01/10/2024 00:00:00</t>
+    <t>01/10/2024</t>
   </si>
   <si>
     <t>TINIKASCHVILI</t>
@@ -385,10 +385,10 @@
     <t>Maka</t>
   </si>
   <si>
-    <t>21/09/1983 00:00:00</t>
-  </si>
-  <si>
-    <t>12/10/2021 00:00:00</t>
+    <t>21/09/1983</t>
+  </si>
+  <si>
+    <t>12/10/2021</t>
   </si>
   <si>
     <t>TONOYAN</t>
@@ -397,13 +397,13 @@
     <t>Alvard</t>
   </si>
   <si>
-    <t>10/01/1963 00:00:00</t>
+    <t>10/01/1963</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>12/01/2016 00:00:00</t>
+    <t>12/01/2016</t>
   </si>
   <si>
     <t>VIUCHE GIRON</t>
@@ -412,13 +412,13 @@
     <t>Sanyi</t>
   </si>
   <si>
-    <t>21/05/1995 00:00:00</t>
+    <t>21/05/1995</t>
   </si>
   <si>
     <t>Colombie</t>
   </si>
   <si>
-    <t>06/03/2025 00:00:00</t>
+    <t>06/03/2025</t>
   </si>
 </sst>
 </file>
@@ -905,7 +905,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79B4D52-D08F-452D-ADD8-793EB28B59C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F2D946-4E1A-423E-8B31-45B9D3C8AB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F2D946-4E1A-423E-8B31-45B9D3C8AB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC52E708-4D92-4D1E-83F8-D14546C1CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC52E708-4D92-4D1E-83F8-D14546C1CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1900EEAD-397B-4434-B9FD-A4AB961F948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_4.xlsx
+++ b/Excel/liste_groupe_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1900EEAD-397B-4434-B9FD-A4AB961F948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8AED01-26D8-4878-8E12-A66F1527DB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
